--- a/ICAP_2Y.xlsx
+++ b/ICAP_2Y.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laced\Desktop\LSEG4Geneviève\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85db7bae6329c353/Documents/Summer Project/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4F3B75-B7D2-4F79-A4D3-5B5B7DC011DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{66E8E49C-73C3-425D-8A00-6DE679554427}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{66E8E49C-73C3-425D-8A00-6DE679554427}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -502,41 +502,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8067056E-0FF4-4E97-B178-D6C1D7FD9C34}">
   <dimension ref="A1:BH400"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="44" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="48" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="56" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="60" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="44" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="48" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="56" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="60" width="20.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,7 +718,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -900,7 +900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46101</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46100</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46099</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46098</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46094</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46093</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46092</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46091</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46090</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46087</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46086</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46085</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46084</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46083</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46080</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46079</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46078</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46077</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46076</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46073</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46072</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46071</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46070</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46069</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46066</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>46065</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>46064</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>46063</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>46062</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>46059</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>46058</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>46057</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>46056</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>46055</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46052</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>46051</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>46050</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>46049</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>46048</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>46045</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>46044</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>46043</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46042</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46041</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46038</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>46037</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>46036</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>46035</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>46034</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>46031</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>46030</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>46029</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="56" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>46028</v>
       </c>
@@ -10728,7 +10728,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="57" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>46027</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>46024</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>46023</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46022</v>
       </c>
@@ -11456,7 +11456,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="61" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>46021</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>46020</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>46017</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>46016</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>46015</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="66" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>46014</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>46013</v>
       </c>
@@ -12730,7 +12730,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="68" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>46010</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="69" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>46009</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="70" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>46008</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>46007</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="72" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>46006</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>46003</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>46002</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="75" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>46001</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="76" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>46000</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="77" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>45999</v>
       </c>
@@ -14550,7 +14550,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>45996</v>
       </c>
@@ -14732,7 +14732,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>45995</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>45994</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>45993</v>
       </c>
@@ -15278,7 +15278,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>45992</v>
       </c>
@@ -15460,7 +15460,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="83" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>45989</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>45988</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>45987</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="86" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>45986</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>45985</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="88" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>45982</v>
       </c>
@@ -16552,7 +16552,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="89" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>45981</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="90" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>45980</v>
       </c>
@@ -16916,7 +16916,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="91" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>45979</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="92" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45978</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="93" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45975</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="94" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>45974</v>
       </c>
@@ -17644,7 +17644,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="95" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>45973</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="96" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>45972</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>45971</v>
       </c>
@@ -18190,7 +18190,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>45968</v>
       </c>
@@ -18372,7 +18372,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>45967</v>
       </c>
@@ -18554,7 +18554,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>45966</v>
       </c>
@@ -18736,7 +18736,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>45965</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>45964</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>45961</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>45960</v>
       </c>
@@ -19464,7 +19464,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>45959</v>
       </c>
@@ -19646,7 +19646,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>45958</v>
       </c>
@@ -19828,7 +19828,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>45957</v>
       </c>
@@ -20010,7 +20010,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>45954</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>45953</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>45952</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>45951</v>
       </c>
@@ -20738,7 +20738,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>45950</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>45947</v>
       </c>
@@ -21102,7 +21102,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>45946</v>
       </c>
@@ -21284,7 +21284,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>45945</v>
       </c>
@@ -21466,7 +21466,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>45944</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>45943</v>
       </c>
@@ -21830,7 +21830,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>45940</v>
       </c>
@@ -22012,7 +22012,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>45939</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>45938</v>
       </c>
@@ -22376,7 +22376,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>45937</v>
       </c>
@@ -22558,7 +22558,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>45936</v>
       </c>
@@ -22740,7 +22740,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>45933</v>
       </c>
@@ -22922,7 +22922,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>45932</v>
       </c>
@@ -23104,7 +23104,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>45931</v>
       </c>
@@ -23286,7 +23286,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>45930</v>
       </c>
@@ -23468,7 +23468,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>45929</v>
       </c>
@@ -23650,7 +23650,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>45926</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>45925</v>
       </c>
@@ -24014,7 +24014,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>45924</v>
       </c>
@@ -24196,7 +24196,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>45923</v>
       </c>
@@ -24378,7 +24378,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>45922</v>
       </c>
@@ -24560,7 +24560,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>45919</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>45918</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>45917</v>
       </c>
@@ -25106,7 +25106,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>45916</v>
       </c>
@@ -25288,7 +25288,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>45915</v>
       </c>
@@ -25470,7 +25470,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>45912</v>
       </c>
@@ -25652,7 +25652,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>45911</v>
       </c>
@@ -25834,7 +25834,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>45910</v>
       </c>
@@ -26016,7 +26016,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>45909</v>
       </c>
@@ -26198,7 +26198,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>45908</v>
       </c>
@@ -26380,7 +26380,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>45905</v>
       </c>
@@ -26562,7 +26562,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>45904</v>
       </c>
@@ -26744,7 +26744,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="145" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>45903</v>
       </c>
@@ -26926,7 +26926,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="146" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>45902</v>
       </c>
@@ -27108,7 +27108,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="147" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>45901</v>
       </c>
@@ -27290,7 +27290,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="148" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>45898</v>
       </c>
@@ -27472,7 +27472,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="149" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>45897</v>
       </c>
@@ -27654,7 +27654,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="150" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>45896</v>
       </c>
@@ -27836,7 +27836,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="151" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>45895</v>
       </c>
@@ -28018,7 +28018,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="152" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>45894</v>
       </c>
@@ -28200,7 +28200,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="153" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>45891</v>
       </c>
@@ -28382,7 +28382,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="154" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>45890</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="155" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>45889</v>
       </c>
@@ -28746,7 +28746,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>45888</v>
       </c>
@@ -28928,7 +28928,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="157" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>45887</v>
       </c>
@@ -29110,7 +29110,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="158" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>45884</v>
       </c>
@@ -29292,7 +29292,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="159" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>45883</v>
       </c>
@@ -29474,7 +29474,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="160" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>45882</v>
       </c>
@@ -29656,7 +29656,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>45881</v>
       </c>
@@ -29838,7 +29838,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>45880</v>
       </c>
@@ -30020,7 +30020,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>45877</v>
       </c>
@@ -30202,7 +30202,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>45876</v>
       </c>
@@ -30384,7 +30384,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>45875</v>
       </c>
@@ -30566,7 +30566,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>45874</v>
       </c>
@@ -30748,7 +30748,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>45873</v>
       </c>
@@ -30930,7 +30930,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>45870</v>
       </c>
@@ -31112,7 +31112,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>45869</v>
       </c>
@@ -31294,7 +31294,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>45868</v>
       </c>
@@ -31476,7 +31476,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>45867</v>
       </c>
@@ -31658,7 +31658,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>45866</v>
       </c>
@@ -31840,7 +31840,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>45863</v>
       </c>
@@ -32022,7 +32022,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>45862</v>
       </c>
@@ -32204,7 +32204,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="175" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>45861</v>
       </c>
@@ -32386,7 +32386,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="176" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>45860</v>
       </c>
@@ -32568,7 +32568,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="177" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>45859</v>
       </c>
@@ -32750,7 +32750,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="178" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>45856</v>
       </c>
@@ -32932,7 +32932,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="179" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>45855</v>
       </c>
@@ -33114,7 +33114,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="180" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>45854</v>
       </c>
@@ -33296,7 +33296,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="181" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>45853</v>
       </c>
@@ -33478,7 +33478,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="182" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>45852</v>
       </c>
@@ -33660,7 +33660,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="183" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>45849</v>
       </c>
@@ -33842,7 +33842,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="184" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>45848</v>
       </c>
@@ -34024,7 +34024,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="185" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>45847</v>
       </c>
@@ -34206,7 +34206,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="186" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>45846</v>
       </c>
@@ -34388,7 +34388,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="187" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>45845</v>
       </c>
@@ -34570,7 +34570,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="188" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>45842</v>
       </c>
@@ -34752,7 +34752,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="189" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>45841</v>
       </c>
@@ -34934,7 +34934,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="190" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>45840</v>
       </c>
@@ -35116,7 +35116,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="191" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>45839</v>
       </c>
@@ -35298,7 +35298,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="192" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>45838</v>
       </c>
@@ -35480,7 +35480,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="193" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>45835</v>
       </c>
@@ -35662,7 +35662,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="194" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>45834</v>
       </c>
@@ -35844,7 +35844,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="195" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>45833</v>
       </c>
@@ -36026,7 +36026,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="196" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>45832</v>
       </c>
@@ -36208,7 +36208,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="197" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>45831</v>
       </c>
@@ -36390,7 +36390,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="198" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>45828</v>
       </c>
@@ -36572,7 +36572,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="199" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>45827</v>
       </c>
@@ -36754,7 +36754,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="200" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>45826</v>
       </c>
@@ -36936,7 +36936,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="201" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>45825</v>
       </c>
@@ -37118,7 +37118,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="202" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>45824</v>
       </c>
@@ -37300,7 +37300,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="203" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>45821</v>
       </c>
@@ -37482,7 +37482,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="204" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>45820</v>
       </c>
@@ -37664,7 +37664,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="205" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>45819</v>
       </c>
@@ -37846,7 +37846,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="206" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>45818</v>
       </c>
@@ -38028,7 +38028,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="207" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>45817</v>
       </c>
@@ -38210,7 +38210,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="208" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>45814</v>
       </c>
@@ -38392,7 +38392,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="209" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>45813</v>
       </c>
@@ -38574,7 +38574,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="210" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>45812</v>
       </c>
@@ -38756,7 +38756,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="211" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>45811</v>
       </c>
@@ -38938,7 +38938,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="212" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>45810</v>
       </c>
@@ -39120,7 +39120,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="213" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>45807</v>
       </c>
@@ -39302,7 +39302,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="214" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>45806</v>
       </c>
@@ -39484,7 +39484,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="215" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>45805</v>
       </c>
@@ -39666,7 +39666,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>45804</v>
       </c>
@@ -39848,7 +39848,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="217" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>45803</v>
       </c>
@@ -40030,7 +40030,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>45800</v>
       </c>
@@ -40212,7 +40212,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="219" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>45799</v>
       </c>
@@ -40394,7 +40394,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="220" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>45798</v>
       </c>
@@ -40576,7 +40576,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="221" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>45797</v>
       </c>
@@ -40758,7 +40758,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="222" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>45796</v>
       </c>
@@ -40940,7 +40940,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="223" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>45793</v>
       </c>
@@ -41122,7 +41122,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="224" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>45792</v>
       </c>
@@ -41304,7 +41304,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="225" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>45791</v>
       </c>
@@ -41486,7 +41486,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="226" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>45790</v>
       </c>
@@ -41668,7 +41668,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="227" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>45789</v>
       </c>
@@ -41850,7 +41850,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="228" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>45786</v>
       </c>
@@ -42032,7 +42032,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="229" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>45785</v>
       </c>
@@ -42214,7 +42214,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="230" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>45784</v>
       </c>
@@ -42396,7 +42396,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="231" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>45783</v>
       </c>
@@ -42578,7 +42578,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="232" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>45782</v>
       </c>
@@ -42760,7 +42760,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="233" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>45779</v>
       </c>
@@ -42942,7 +42942,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="234" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>45778</v>
       </c>
@@ -43124,7 +43124,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="235" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>45777</v>
       </c>
@@ -43306,7 +43306,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="236" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>45776</v>
       </c>
@@ -43488,7 +43488,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="237" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>45775</v>
       </c>
@@ -43670,7 +43670,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="238" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>45772</v>
       </c>
@@ -43852,7 +43852,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="239" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>45771</v>
       </c>
@@ -44034,7 +44034,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="240" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>45770</v>
       </c>
@@ -44216,7 +44216,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="241" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>45769</v>
       </c>
@@ -44398,7 +44398,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="242" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>45768</v>
       </c>
@@ -44580,7 +44580,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="243" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>45765</v>
       </c>
@@ -44762,7 +44762,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="244" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>45764</v>
       </c>
@@ -44944,7 +44944,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="245" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>45763</v>
       </c>
@@ -45126,7 +45126,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="246" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>45762</v>
       </c>
@@ -45308,7 +45308,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="247" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>45761</v>
       </c>
@@ -45490,7 +45490,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="248" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>45758</v>
       </c>
@@ -45672,7 +45672,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>45757</v>
       </c>
@@ -45854,7 +45854,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="250" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>45756</v>
       </c>
@@ -46036,7 +46036,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="251" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>45755</v>
       </c>
@@ -46218,7 +46218,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="252" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>45754</v>
       </c>
@@ -46400,7 +46400,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="253" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>45751</v>
       </c>
@@ -46582,7 +46582,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="254" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>45750</v>
       </c>
@@ -46764,7 +46764,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="255" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>45749</v>
       </c>
@@ -46946,7 +46946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>45748</v>
       </c>
@@ -47128,7 +47128,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="257" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>45747</v>
       </c>
@@ -47310,7 +47310,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="258" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>45744</v>
       </c>
@@ -47492,7 +47492,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="259" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>45743</v>
       </c>
@@ -47674,7 +47674,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="260" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>45742</v>
       </c>
@@ -47856,7 +47856,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="261" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>45741</v>
       </c>
@@ -48038,7 +48038,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="262" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>45740</v>
       </c>
@@ -48220,7 +48220,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="263" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>45737</v>
       </c>
@@ -48402,7 +48402,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="264" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>45736</v>
       </c>
@@ -48584,7 +48584,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="265" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>45735</v>
       </c>
@@ -48766,7 +48766,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="266" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>45734</v>
       </c>
@@ -48948,7 +48948,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="267" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>45733</v>
       </c>
@@ -49130,7 +49130,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="268" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>45730</v>
       </c>
@@ -49312,7 +49312,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="269" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>45729</v>
       </c>
@@ -49494,7 +49494,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="270" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>45728</v>
       </c>
@@ -49676,7 +49676,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="271" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>45727</v>
       </c>
@@ -49858,7 +49858,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="272" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>45726</v>
       </c>
@@ -50040,7 +50040,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="273" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>45723</v>
       </c>
@@ -50222,7 +50222,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="274" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>45722</v>
       </c>
@@ -50404,7 +50404,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="275" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>45721</v>
       </c>
@@ -50586,7 +50586,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="276" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>45720</v>
       </c>
@@ -50768,7 +50768,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="277" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>45719</v>
       </c>
@@ -50950,7 +50950,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>45716</v>
       </c>
@@ -51132,7 +51132,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="279" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>45715</v>
       </c>
@@ -51314,7 +51314,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="280" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>45714</v>
       </c>
@@ -51496,7 +51496,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="281" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>45713</v>
       </c>
@@ -51678,7 +51678,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="282" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>45712</v>
       </c>
@@ -51860,7 +51860,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="283" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>45709</v>
       </c>
@@ -52042,7 +52042,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="284" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>45708</v>
       </c>
@@ -52224,7 +52224,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="285" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>45707</v>
       </c>
@@ -52406,7 +52406,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="286" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>45706</v>
       </c>
@@ -52588,7 +52588,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="287" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>45705</v>
       </c>
@@ -52770,7 +52770,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="288" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>45702</v>
       </c>
@@ -52952,7 +52952,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="289" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>45701</v>
       </c>
@@ -53134,7 +53134,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="290" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>45700</v>
       </c>
@@ -53316,7 +53316,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="291" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>45699</v>
       </c>
@@ -53498,7 +53498,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="292" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>45698</v>
       </c>
@@ -53680,7 +53680,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="293" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>45695</v>
       </c>
@@ -53862,7 +53862,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="294" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>45694</v>
       </c>
@@ -54044,7 +54044,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="295" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>45693</v>
       </c>
@@ -54226,7 +54226,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="296" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>45692</v>
       </c>
@@ -54408,7 +54408,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="297" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>45691</v>
       </c>
@@ -54590,7 +54590,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="298" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>45688</v>
       </c>
@@ -54772,7 +54772,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="299" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>45687</v>
       </c>
@@ -54954,7 +54954,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="300" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>45686</v>
       </c>
@@ -55136,7 +55136,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="301" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>45685</v>
       </c>
@@ -55318,7 +55318,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="302" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>45684</v>
       </c>
@@ -55500,7 +55500,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="303" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>45681</v>
       </c>
@@ -55682,7 +55682,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="304" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>45680</v>
       </c>
@@ -55864,7 +55864,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="305" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>45679</v>
       </c>
@@ -56046,7 +56046,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="306" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>45678</v>
       </c>
@@ -56228,7 +56228,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="307" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>45677</v>
       </c>
@@ -56410,7 +56410,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="308" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>45674</v>
       </c>
@@ -56592,7 +56592,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="309" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>45673</v>
       </c>
@@ -56774,7 +56774,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="310" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>45672</v>
       </c>
@@ -56956,7 +56956,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="311" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>45671</v>
       </c>
@@ -57138,7 +57138,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="312" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>45670</v>
       </c>
@@ -57320,7 +57320,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="313" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>45667</v>
       </c>
@@ -57502,7 +57502,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="314" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>45666</v>
       </c>
@@ -57684,7 +57684,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="315" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>45665</v>
       </c>
@@ -57866,7 +57866,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="316" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>45664</v>
       </c>
@@ -58048,7 +58048,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="317" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>45663</v>
       </c>
@@ -58230,7 +58230,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="318" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>45660</v>
       </c>
@@ -58412,7 +58412,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="319" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>45659</v>
       </c>
@@ -58594,7 +58594,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="320" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>45657</v>
       </c>
@@ -58776,7 +58776,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="321" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>45656</v>
       </c>
@@ -58958,7 +58958,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="322" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>45653</v>
       </c>
@@ -59140,7 +59140,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="323" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>45652</v>
       </c>
@@ -59322,7 +59322,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="324" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>45651</v>
       </c>
@@ -59504,7 +59504,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="325" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>45650</v>
       </c>
@@ -59686,7 +59686,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="326" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>45649</v>
       </c>
@@ -59868,7 +59868,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="327" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>45646</v>
       </c>
@@ -60050,7 +60050,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="328" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>45645</v>
       </c>
@@ -60232,7 +60232,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="329" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>45644</v>
       </c>
@@ -60414,7 +60414,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="330" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>45643</v>
       </c>
@@ -60596,7 +60596,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="331" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>45642</v>
       </c>
@@ -60778,7 +60778,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="332" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>45639</v>
       </c>
@@ -60960,7 +60960,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="333" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>45638</v>
       </c>
@@ -61142,7 +61142,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="334" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>45637</v>
       </c>
@@ -61324,7 +61324,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="335" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>45636</v>
       </c>
@@ -61506,7 +61506,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="336" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>45635</v>
       </c>
@@ -61688,7 +61688,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="337" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>45632</v>
       </c>
@@ -61870,7 +61870,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="338" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>45631</v>
       </c>
@@ -62052,7 +62052,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="339" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>45630</v>
       </c>
@@ -62234,7 +62234,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="340" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>45629</v>
       </c>
@@ -62416,7 +62416,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="341" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>45628</v>
       </c>
@@ -62598,7 +62598,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="342" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>45625</v>
       </c>
@@ -62780,7 +62780,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="343" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>45624</v>
       </c>
@@ -62962,7 +62962,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="344" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>45623</v>
       </c>
@@ -63144,7 +63144,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="345" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>45622</v>
       </c>
@@ -63326,7 +63326,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="346" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>45621</v>
       </c>
@@ -63508,7 +63508,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="347" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>45618</v>
       </c>
@@ -63690,7 +63690,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="348" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>45617</v>
       </c>
@@ -63872,7 +63872,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="349" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>45616</v>
       </c>
@@ -64054,7 +64054,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="350" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>45615</v>
       </c>
@@ -64236,7 +64236,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="351" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>45614</v>
       </c>
@@ -64418,7 +64418,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="352" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>45611</v>
       </c>
@@ -64600,7 +64600,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="353" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>45610</v>
       </c>
@@ -64782,7 +64782,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="354" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>45609</v>
       </c>
@@ -64964,7 +64964,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="355" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>45608</v>
       </c>
@@ -65146,7 +65146,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="356" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>45607</v>
       </c>
@@ -65328,7 +65328,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="357" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>45604</v>
       </c>
@@ -65510,7 +65510,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="358" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>45603</v>
       </c>
@@ -65692,7 +65692,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="359" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>45602</v>
       </c>
@@ -65874,7 +65874,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="360" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>45601</v>
       </c>
@@ -66056,7 +66056,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="361" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>45600</v>
       </c>
@@ -66238,7 +66238,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="362" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>45597</v>
       </c>
@@ -66420,7 +66420,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="363" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>45596</v>
       </c>
@@ -66602,7 +66602,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="364" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>45595</v>
       </c>
@@ -66784,7 +66784,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="365" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>45594</v>
       </c>
@@ -66966,7 +66966,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="366" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>45593</v>
       </c>
@@ -67148,7 +67148,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="367" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>45590</v>
       </c>
@@ -67330,7 +67330,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="368" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>45589</v>
       </c>
@@ -67512,7 +67512,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="369" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>45588</v>
       </c>
@@ -67694,7 +67694,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="370" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>45587</v>
       </c>
@@ -67876,7 +67876,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="371" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>45586</v>
       </c>
@@ -68058,7 +68058,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="372" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>45583</v>
       </c>
@@ -68240,7 +68240,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="373" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>45582</v>
       </c>
@@ -68422,7 +68422,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="374" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>45581</v>
       </c>
@@ -68604,7 +68604,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="375" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>45580</v>
       </c>
@@ -68786,7 +68786,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="376" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>45579</v>
       </c>
@@ -68968,7 +68968,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="377" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>45576</v>
       </c>
@@ -69150,7 +69150,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="378" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>45575</v>
       </c>
@@ -69332,7 +69332,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="379" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>45574</v>
       </c>
@@ -69514,7 +69514,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="380" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>45573</v>
       </c>
@@ -69696,7 +69696,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="381" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>45572</v>
       </c>
@@ -69878,7 +69878,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="382" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>45569</v>
       </c>
@@ -70060,7 +70060,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="383" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>45568</v>
       </c>
@@ -70242,7 +70242,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="384" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>45567</v>
       </c>
@@ -70424,7 +70424,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="385" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>45566</v>
       </c>
@@ -70606,7 +70606,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="386" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>45565</v>
       </c>
@@ -70788,7 +70788,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="387" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>45562</v>
       </c>
@@ -70970,7 +70970,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="388" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>45561</v>
       </c>
@@ -71152,7 +71152,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="389" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>45560</v>
       </c>
@@ -71334,7 +71334,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="390" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>45559</v>
       </c>
@@ -71516,7 +71516,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="391" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>45558</v>
       </c>
@@ -71698,7 +71698,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="392" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>45555</v>
       </c>
@@ -71880,7 +71880,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="393" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>45554</v>
       </c>
@@ -72062,7 +72062,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="394" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>45553</v>
       </c>
@@ -72244,7 +72244,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="395" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>45552</v>
       </c>
@@ -72426,7 +72426,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="396" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>45551</v>
       </c>
@@ -72608,7 +72608,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="397" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>45548</v>
       </c>
@@ -72790,7 +72790,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="398" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>45547</v>
       </c>
@@ -72972,7 +72972,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="399" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>45546</v>
       </c>
@@ -73154,7 +73154,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="400" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>45545</v>
       </c>
